--- a/artfynd/A 36756-2023 artfynd.xlsx
+++ b/artfynd/A 36756-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36756-2023 artfynd.xlsx
+++ b/artfynd/A 36756-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112241810</v>
+        <v>112241824</v>
       </c>
       <c r="B2" t="n">
         <v>56461</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556453</v>
+        <v>556616</v>
       </c>
       <c r="R2" t="n">
-        <v>7019706</v>
+        <v>7020043</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112241824</v>
+        <v>112241822</v>
       </c>
       <c r="B3" t="n">
         <v>56461</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556616</v>
+        <v>556588</v>
       </c>
       <c r="R3" t="n">
-        <v>7020043</v>
+        <v>7020141</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112241812</v>
+        <v>112241834</v>
       </c>
       <c r="B4" t="n">
-        <v>56461</v>
+        <v>89612</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,38 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>gäddvattenbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556465</v>
+        <v>556608</v>
       </c>
       <c r="R4" t="n">
-        <v>7019795</v>
+        <v>7020190</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112241822</v>
+        <v>112241826</v>
       </c>
       <c r="B5" t="n">
         <v>56461</v>
@@ -1052,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556588</v>
+        <v>556638</v>
       </c>
       <c r="R5" t="n">
-        <v>7020141</v>
+        <v>7020040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112241834</v>
+        <v>112241830</v>
       </c>
       <c r="B6" t="n">
-        <v>89612</v>
+        <v>56461</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,34 +1126,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>gäddvattenbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556608</v>
+        <v>556606</v>
       </c>
       <c r="R6" t="n">
-        <v>7020190</v>
+        <v>7019898</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1190,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112241826</v>
+        <v>112241823</v>
       </c>
       <c r="B7" t="n">
         <v>56461</v>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556638</v>
+        <v>556568</v>
       </c>
       <c r="R7" t="n">
-        <v>7020040</v>
+        <v>7020117</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112241830</v>
+        <v>112241818</v>
       </c>
       <c r="B8" t="n">
         <v>56461</v>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556606</v>
+        <v>556678</v>
       </c>
       <c r="R8" t="n">
-        <v>7019898</v>
+        <v>7020120</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112241823</v>
+        <v>112241827</v>
       </c>
       <c r="B9" t="n">
         <v>56461</v>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556568</v>
+        <v>556622</v>
       </c>
       <c r="R9" t="n">
-        <v>7020117</v>
+        <v>7020033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112241809</v>
+        <v>112241829</v>
       </c>
       <c r="B10" t="n">
         <v>56461</v>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556345</v>
+        <v>556596</v>
       </c>
       <c r="R10" t="n">
-        <v>7019567</v>
+        <v>7019914</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112241818</v>
+        <v>112241814</v>
       </c>
       <c r="B11" t="n">
         <v>56461</v>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556678</v>
+        <v>556620</v>
       </c>
       <c r="R11" t="n">
-        <v>7020120</v>
+        <v>7019951</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1776,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112241808</v>
+        <v>112241821</v>
       </c>
       <c r="B12" t="n">
         <v>56461</v>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556337</v>
+        <v>556594</v>
       </c>
       <c r="R12" t="n">
-        <v>7019554</v>
+        <v>7020159</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,7 +1887,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112241827</v>
+        <v>112241817</v>
       </c>
       <c r="B13" t="n">
         <v>56461</v>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556622</v>
+        <v>556671</v>
       </c>
       <c r="R13" t="n">
-        <v>7020033</v>
+        <v>7020090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,7 +1998,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112241829</v>
+        <v>112241828</v>
       </c>
       <c r="B14" t="n">
         <v>56461</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556596</v>
+        <v>556601</v>
       </c>
       <c r="R14" t="n">
         <v>7019914</v>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,790 +2106,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>112241814</v>
-      </c>
-      <c r="B15" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>gäddvattenbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>556620</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7019951</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>112241821</v>
-      </c>
-      <c r="B16" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>gäddvattenbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>556594</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7020159</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>112241817</v>
-      </c>
-      <c r="B17" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>gäddvattenbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>556671</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7020090</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>112241811</v>
-      </c>
-      <c r="B18" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>gäddvattenbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>556434</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7019723</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>112241828</v>
-      </c>
-      <c r="B19" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>gäddvattenbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>556601</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7019914</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>112241832</v>
-      </c>
-      <c r="B20" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>gäddvattenbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>556328</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7019537</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>112241807</v>
-      </c>
-      <c r="B21" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>gäddvattenbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>556319</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7019532</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36756-2023 artfynd.xlsx
+++ b/artfynd/A 36756-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112241824</v>
+        <v>112241814</v>
       </c>
       <c r="B2" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556616</v>
+        <v>556620</v>
       </c>
       <c r="R2" t="n">
-        <v>7020043</v>
+        <v>7019951</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112241822</v>
+        <v>112241815</v>
       </c>
       <c r="B3" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556588</v>
+        <v>556683</v>
       </c>
       <c r="R3" t="n">
-        <v>7020141</v>
+        <v>7020061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112241834</v>
+        <v>112241816</v>
       </c>
       <c r="B4" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,34 +898,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>gäddvattenbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556608</v>
+        <v>556675</v>
       </c>
       <c r="R4" t="n">
-        <v>7020190</v>
+        <v>7020050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +962,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112241826</v>
+        <v>112241817</v>
       </c>
       <c r="B5" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556638</v>
+        <v>556672</v>
       </c>
       <c r="R5" t="n">
-        <v>7020040</v>
+        <v>7020090</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1072,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112241830</v>
+        <v>112241818</v>
       </c>
       <c r="B6" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556606</v>
+        <v>556678</v>
       </c>
       <c r="R6" t="n">
-        <v>7019898</v>
+        <v>7020120</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112241823</v>
+        <v>112241821</v>
       </c>
       <c r="B7" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556568</v>
+        <v>556593</v>
       </c>
       <c r="R7" t="n">
-        <v>7020117</v>
+        <v>7020159</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1284,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112241818</v>
+        <v>112241822</v>
       </c>
       <c r="B8" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556678</v>
+        <v>556588</v>
       </c>
       <c r="R8" t="n">
-        <v>7020120</v>
+        <v>7020141</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112241827</v>
+        <v>112241823</v>
       </c>
       <c r="B9" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556622</v>
+        <v>556568</v>
       </c>
       <c r="R9" t="n">
-        <v>7020033</v>
+        <v>7020118</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,15 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112241829</v>
+        <v>112241824</v>
       </c>
       <c r="B10" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556596</v>
+        <v>556616</v>
       </c>
       <c r="R10" t="n">
-        <v>7019914</v>
+        <v>7020043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1602,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,15 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112241814</v>
+        <v>112241826</v>
       </c>
       <c r="B11" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556620</v>
+        <v>556638</v>
       </c>
       <c r="R11" t="n">
-        <v>7019951</v>
+        <v>7020039</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112241821</v>
+        <v>112241827</v>
       </c>
       <c r="B12" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556594</v>
+        <v>556622</v>
       </c>
       <c r="R12" t="n">
-        <v>7020159</v>
+        <v>7020033</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1814,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,15 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112241817</v>
+        <v>112241828</v>
       </c>
       <c r="B13" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556671</v>
+        <v>556601</v>
       </c>
       <c r="R13" t="n">
-        <v>7020090</v>
+        <v>7019914</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,7 +1920,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,15 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112241828</v>
+        <v>112241829</v>
       </c>
       <c r="B14" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +1986,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556601</v>
+        <v>556596</v>
       </c>
       <c r="R14" t="n">
         <v>7019914</v>
@@ -2082,7 +2026,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,6 +2050,112 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112241830</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>gäddvattenbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>556606</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7019898</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36756-2023 artfynd.xlsx
+++ b/artfynd/A 36756-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241814</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241815</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241816</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241818</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241821</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241822</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241823</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241824</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241826</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241827</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241828</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241829</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,8 +2226,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241830</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>